--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_361_Indonesia_Eastern.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_361_Indonesia_Eastern.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Raa429b823f79404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R40d0f086dabc4890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R928fadf76a094393"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9ca59a268130460a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re9d55a8a5cd54206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5e850b1d83b84307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re4812c31fdba4f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0abb8b9717f84158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rbb567221fd5c4529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3a307007b71142dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R375fa40c2189449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R66e04c492bf847c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ361CommercialTable" displayName="EEZ361CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ361CommercialTable" displayName="EEZ361CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ361FunctionalTable" displayName="EEZ361FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ361FunctionalTable" displayName="EEZ361FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ361ValidationTable" displayName="EEZ361ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ361ValidationTable" displayName="EEZ361ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10476,7 +10430,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7e1faea88d442a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab397eb12c984aea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10486,20 +10440,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10507,606 +10451,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>140812.7032901943</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.431052878003553</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>269.8067918681589</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>140812.7032901943</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>271.0636255544021</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$147,A2,'Species'!$U$2:$U$147))</x:f>
-        <x:v>38169201.87795635</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.431052878003553</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>269.8067918681589</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>37992223.72901027</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>176978.14894608408</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0046582729720805</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0046582729720805035</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>192048.3197318681</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.901787510863303</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>79.76043444612739</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>192048.3197318681</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>111.40632056177049</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$147,A3,'Species'!$U$2:$U$147))</x:f>
-        <x:v>21395396.67139789</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.901787510863303</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>79.76043444612739</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>15317857.41646258</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>6077539.254935311</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.3967617069214648</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.39676170692146473</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>72.6317794552</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.489424805103009</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>308.62052456702514</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>72.6317794552</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>469.34038965304234</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$147,A4,'Species'!$U$2:$U$147))</x:f>
-        <x:v>34089.027670697404</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.489424805103009</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>308.62052456702514</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>22415.657875700304</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>11673.3697949971</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.5207685565031583</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.5207685565031583</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>254608.1745545337</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.74166097915482</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>55.164664235886036</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>254608.1745545337</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>101.23640882827601</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$147,A5,'Species'!$U$2:$U$147))</x:f>
-        <x:v>25775617.250223834</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.74166097915482</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>55.164664235886036</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>14045374.461012714</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>11730242.78921112</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.8351676789943936</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.8351676789943936</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>44662.411202051604</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0777509329021258</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>11.960543995490292</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>44662.411202051604</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.0156781593609</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$147,A6,'Species'!$U$2:$U$147))</x:f>
-        <x:v>536649.1588248871</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0777509329021258</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>11.960543995490292</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>534186.7341268167</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2462.42469807039</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0046096702534095</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.004609670253409563</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>869225.4907250778</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2931835710521393</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>196.4190341018944</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>869225.4907250778</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>206.04922650112783</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$147,A7,'Species'!$U$2:$U$147))</x:f>
-        <x:v>179103240.01896554</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2931835710521393</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>196.4190341018944</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>170732431.30496496</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8370808.714000583</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0490288145610045</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.049028814561004594</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1697643.320174324</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.656836076538628</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>453.77030975437737</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1697643.320174324</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>821.8845124966651</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$147,A8,'Species'!$U$2:$U$147))</x:f>
-        <x:v>1395266752.5946944</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.656836076538628</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>453.77030975437737</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>770340135.2479527</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>624926617.3467417</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8112346595385347</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8112346595385347</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1371.9593065553</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1371.9593065553</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$147,A9,'Species'!$U$2:$U$147))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1089786.0140896204</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>1089786.0140896204</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>20503.1914865483</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.242842727231571</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1749.2131244871625</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>20503.1914865483</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1780.2003396792352</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$147,A10,'Species'!$U$2:$U$147))</x:f>
-        <x:v>36499788.44886169</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.242842727231571</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1749.2131244871625</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>35864451.64214374</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>635336.8067179471</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.017714945513662</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.017714945513662143</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>161605.33183783496</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.386052295403011</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2432.496899617951</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>161605.33183783496</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2448.3867550675554</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$147,A11,'Species'!$U$2:$U$147))</x:f>
-        <x:v>395672354.02005225</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.386052295403011</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2432.496899617951</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>393104468.6572637</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2567885.362788558</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0065323230019738</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.006532323001973865</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e1808879e9b4375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb79a7066ae404a28"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11116,20 +10666,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11137,1092 +10677,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2524.8235617831</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9661731207319044</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>925.0668554260587</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2524.8235617831</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>995.0298814083905</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$147,A2,'Species'!$U$2:$U$147))</x:f>
-        <x:v>2512274.889258148</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9661731207319044</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>925.0668554260587</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2335630.5928043136</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>176644.2964538345</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0756302375033304</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07563023750333035</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5943.4012536451</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.459999999999999</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5943.4012536451</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.4031503126605</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$147,A3,'Species'!$U$2:$U$147))</x:f>
-        <x:v>1714095.6451234627</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.459999999999999</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1714095.6451234596</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3.026798367500305e-9</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000000000000018</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.7658281649051717e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>52945.126890595406</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.156751071650817</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1434.6668771360673</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>52945.126890595406</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1436.4376582290715</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$147,A4,'Species'!$U$2:$U$147))</x:f>
-        <x:v>76052374.0853679</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.156751071650817</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1434.6668771360673</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>75958619.85570334</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>93754.22966456413</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.001234280320557</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0012342803205569908</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>167698.9822073106</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.084967864706853</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1216.096013208404</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>167698.9822073106</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1619.6487132164343</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$147,A5,'Species'!$U$2:$U$147))</x:f>
-        <x:v>271613440.7397763</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.084967864706853</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1216.096013208404</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>203938063.6814175</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>67675377.05835882</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3318427949972014</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3318427949972013</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>133278.22116495462</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.4840935771964014</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3048.551788665374</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>133278.22116495462</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3057.3795637997428</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$147,A6,'Species'!$U$2:$U$147))</x:f>
-        <x:v>407482109.6893146</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.4840935771964014</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3048.551788665374</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>406305559.52256167</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1176550.1667529345</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0028957274621972</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.002895727462197332</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>195.95306477309998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4226596754009613</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>264.6425517084222</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>195.95306477309998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>275.63262288902854</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$147,A7,'Species'!$U$2:$U$147))</x:f>
-        <x:v>54011.05720655325</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4226596754009613</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>264.6425517084222</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>51857.51907663892</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2153.5381299143264</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0415279822147232</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.041527982214723126</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>20307.2384217752</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.250757017660586</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1781.3818276986628</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>20307.2384217752</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1794.7185449191743</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$147,A8,'Species'!$U$2:$U$147))</x:f>
-        <x:v>36445777.39165514</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.250757017660586</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1781.3818276986628</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>36174945.495294414</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>270831.89636072516</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0074867257615068</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0074867257615068026</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>53442.8296978046</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4154090087198994</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>260.260948809061</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>53442.8296978046</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>265.4582292902351</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$147,A9,'Species'!$U$2:$U$147))</x:f>
-        <x:v>14186838.9398388</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4154090087198994</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>260.260948809061</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>13909081.564191688</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>277757.3756471127</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0199694979402656</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.019969497940265642</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>68689.4608595995</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.0935356701550485</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>124.03254932927837</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>68689.4608595995</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>135.71625882112323</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$147,A10,'Species'!$U$2:$U$147))</x:f>
-        <x:v>9322276.648304818</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.0935356701550485</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>124.03254932927837</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8519728.94246981</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>802547.705835009</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0941987369849768</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09419873698497691</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>796844.491991622</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.317407451781249</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>207.6861099002946</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>796844.491991622</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>223.68441540898405</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$147,A11,'Species'!$U$2:$U$147))</x:f>
-        <x:v>178241694.36301485</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.317407451781249</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>207.6861099002946</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>165493532.73721644</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>12748161.625798404</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0770311770795353</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.07703117707953537</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>785527.3741092623</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5089450519038987</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>322.8085669865809</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>785527.3741092623</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>692.3426847424546</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$147,A12,'Species'!$U$2:$U$147))</x:f>
-        <x:v>543854131.1294972</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5089450519038987</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>322.8085669865809</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>253574965.96494278</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>290279165.16455436</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>2.144746935329121</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.1447469353291209</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>350791.7349699881</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6384142201381096</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>434.9248477775412</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>350791.7349699881</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>732.4129272971728</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$147,A13,'Species'!$U$2:$U$147))</x:f>
-        <x:v>256924401.481023</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6384142201381096</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>434.9248477775412</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>152568041.93344164</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>104356359.54758137</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.6839988127599306</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.6839988127599305</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>44703.9965662468</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.07807860843156</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>11.969571640631138</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>44703.9965662468</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>12.029538401082824</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$147,A14,'Species'!$U$2:$U$147))</x:f>
-        <x:v>537768.4433755407</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.07807860843156</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>11.969571640631138</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>535087.6895222195</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2680.753853321192</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0050099337095848</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.005009933709584761</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>138605.49003406352</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.70374783557818</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>50.55310502582049</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>138605.49003406352</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>52.00773598352805</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$147,A15,'Species'!$U$2:$U$147))</x:f>
-        <x:v>7208557.731559104</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.70374783557818</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>50.55310502582049</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>7006937.894847329</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>201619.8367117755</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0287743147916353</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.028774314791635315</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>48430.7889588707</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.225715459636806</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>168.15719704461017</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>48430.7889588707</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>169.15673712177895</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$147,A16,'Species'!$U$2:$U$147))</x:f>
-        <x:v>8192394.2365160445</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.225715459636806</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>168.15719704461017</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>8143985.72198275</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>48408.514533294365</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.00594408145911</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.005944081459110016</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>134675.0438589322</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.7737203460716224</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>593.9096010513387</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>134675.0438589322</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>621.7260018856468</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$147,A17,'Species'!$U$2:$U$147))</x:f>
-        <x:v>83730976.57218805</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.7737203460716224</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>593.9096010513387</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>79984801.56982996</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3746175.002358094</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0468360854666563</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.04683608546665621</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>534161.7683823823</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.185554729532312</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>153.30443875323283</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>534161.7683823823</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>270.1633184551087</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$147,A18,'Species'!$U$2:$U$147))</x:f>
-        <x:v>144310915.93803358</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.185554729532312</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>153.30443875323283</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>81889370.10529548</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>62421545.8327381</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.7622667722620757</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.7622667722620757</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>43714.1763153794</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>4.065757320360866</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>1163.4757085353122</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>43714.1763153794</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>1169.5232847387967</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$147,A19,'Species'!$U$2:$U$147))</x:f>
-        <x:v>51124747.07401343</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>4.065757320360866</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>1163.4757085353122</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>50860382.26157361</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>264364.8124398142</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0051978534309907</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.005197853430990607</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>72.6317794552</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.489424805103009</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>308.62052456702514</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>72.6317794552</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>469.34038965304234</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$147,A20,'Species'!$U$2:$U$147))</x:f>
-        <x:v>34089.027670697404</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.489424805103009</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>308.62052456702514</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>22415.657875700304</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>11673.3697949971</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.5207685565031583</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.5207685565031583</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reac5bf5361ea4f0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra924655897bb41a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12397,7 +11228,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12496,7 +11327,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2093542875.0827374</x:v>
+        <x:v>1439043330.8649027</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12510,7 +11341,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2093542875.0827374</x:v>
+        <x:v>1548987104.3551705</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12524,7 +11355,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-654499544.2178347</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12538,7 +11369,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-544555770.727567</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12549,9 +11380,9 @@
         <x:v>EEZ_361</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12563,47 +11394,19 @@
         <x:v>EEZ_361</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_361</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_361</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6da06ae137d94d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09dc3611033542dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12650,7 +11453,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
